--- a/tests/fixtures/tne_planted/data/Travel_Requests_Without_Expense.xlsx
+++ b/tests/fixtures/tne_planted/data/Travel_Requests_Without_Expense.xlsx
@@ -34,39 +34,39 @@
     <t>Wong, Kelly</t>
   </si>
   <si>
+    <t>Costa, Bruno</t>
+  </si>
+  <si>
+    <t>Ibrahim, Yusuf</t>
+  </si>
+  <si>
+    <t>Larsen, Freya</t>
+  </si>
+  <si>
+    <t>Singh, Manpreet</t>
+  </si>
+  <si>
+    <t>Osei, Kwame</t>
+  </si>
+  <si>
+    <t>Fischer, Lena</t>
+  </si>
+  <si>
     <t>Alvarez, Diego</t>
   </si>
   <si>
+    <t>Patel, Nisha</t>
+  </si>
+  <si>
+    <t>Haddad, Omar</t>
+  </si>
+  <si>
+    <t>Novak, Petra</t>
+  </si>
+  <si>
     <t>Dubois, Camille</t>
   </si>
   <si>
-    <t>Fischer, Lena</t>
-  </si>
-  <si>
-    <t>Osei, Kwame</t>
-  </si>
-  <si>
-    <t>Singh, Manpreet</t>
-  </si>
-  <si>
-    <t>Haddad, Omar</t>
-  </si>
-  <si>
-    <t>Novak, Petra</t>
-  </si>
-  <si>
-    <t>Costa, Bruno</t>
-  </si>
-  <si>
-    <t>Ibrahim, Yusuf</t>
-  </si>
-  <si>
-    <t>Patel, Nisha</t>
-  </si>
-  <si>
-    <t>Larsen, Freya</t>
-  </si>
-  <si>
     <t>Chen, Alex</t>
   </si>
   <si>
@@ -835,13 +835,13 @@
     <t>TRQ-31A-N16</t>
   </si>
   <si>
+    <t>Draft</t>
+  </si>
+  <si>
+    <t>Submitted</t>
+  </si>
+  <si>
     <t>Sent Back to Employee</t>
-  </si>
-  <si>
-    <t>Draft</t>
-  </si>
-  <si>
-    <t>Submitted</t>
   </si>
   <si>
     <t>Approved</t>
@@ -1316,10 +1316,10 @@
         <v>273</v>
       </c>
       <c r="D2" s="1">
-        <v>46120</v>
+        <v>46119</v>
       </c>
       <c r="E2">
-        <v>1252.17</v>
+        <v>1896.45</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1333,10 +1333,10 @@
         <v>274</v>
       </c>
       <c r="D3" s="1">
-        <v>46012</v>
+        <v>46048</v>
       </c>
       <c r="E3">
-        <v>2082.41</v>
+        <v>1905.81</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1347,13 +1347,13 @@
         <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D4" s="1">
-        <v>45903</v>
+        <v>46093</v>
       </c>
       <c r="E4">
-        <v>1790.26</v>
+        <v>729.58</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1364,13 +1364,13 @@
         <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D5" s="1">
-        <v>45750</v>
+        <v>46141</v>
       </c>
       <c r="E5">
-        <v>1235.87</v>
+        <v>567.1900000000001</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1381,18 +1381,18 @@
         <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D6" s="1">
-        <v>46022</v>
+        <v>45819</v>
       </c>
       <c r="E6">
-        <v>1288.96</v>
+        <v>1982.78</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>36</v>
@@ -1401,49 +1401,49 @@
         <v>275</v>
       </c>
       <c r="D7" s="1">
-        <v>45889</v>
+        <v>45920</v>
       </c>
       <c r="E7">
-        <v>1652.61</v>
+        <v>121.36</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D8" s="1">
-        <v>45977</v>
+        <v>45868</v>
       </c>
       <c r="E8">
-        <v>1018.82</v>
+        <v>394.74</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D9" s="1">
-        <v>45764</v>
+        <v>46090</v>
       </c>
       <c r="E9">
-        <v>1521.59</v>
+        <v>1353.46</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>39</v>
@@ -1452,10 +1452,10 @@
         <v>274</v>
       </c>
       <c r="D10" s="1">
-        <v>45687</v>
+        <v>45720</v>
       </c>
       <c r="E10">
-        <v>550.76</v>
+        <v>918.76</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1466,35 +1466,35 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D11" s="1">
-        <v>45824</v>
+        <v>45924</v>
       </c>
       <c r="E11">
-        <v>2493.3</v>
+        <v>1407.03</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
         <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D12" s="1">
-        <v>46122</v>
+        <v>46049</v>
       </c>
       <c r="E12">
-        <v>226.63</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
         <v>42</v>
@@ -1503,15 +1503,15 @@
         <v>274</v>
       </c>
       <c r="D13" s="1">
-        <v>46133</v>
+        <v>45747</v>
       </c>
       <c r="E13">
-        <v>264.98</v>
+        <v>2107.28</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
         <v>43</v>
@@ -1520,32 +1520,32 @@
         <v>273</v>
       </c>
       <c r="D14" s="1">
-        <v>45955</v>
+        <v>45925</v>
       </c>
       <c r="E14">
-        <v>2146.24</v>
+        <v>1511.72</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D15" s="1">
-        <v>45743</v>
+        <v>45978</v>
       </c>
       <c r="E15">
-        <v>2622.2</v>
+        <v>1225.41</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B16" t="s">
         <v>45</v>
@@ -1554,32 +1554,32 @@
         <v>274</v>
       </c>
       <c r="D16" s="1">
-        <v>46013</v>
+        <v>45756</v>
       </c>
       <c r="E16">
-        <v>1521.39</v>
+        <v>2817.52</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17" t="s">
         <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D17" s="1">
-        <v>45664</v>
+        <v>45751</v>
       </c>
       <c r="E17">
-        <v>228.33</v>
+        <v>1768.78</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
         <v>47</v>
@@ -1588,15 +1588,15 @@
         <v>273</v>
       </c>
       <c r="D18" s="1">
-        <v>46035</v>
+        <v>46136</v>
       </c>
       <c r="E18">
-        <v>1360.27</v>
+        <v>535.85</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
         <v>48</v>
@@ -1605,66 +1605,66 @@
         <v>273</v>
       </c>
       <c r="D19" s="1">
-        <v>45858</v>
+        <v>46001</v>
       </c>
       <c r="E19">
-        <v>1184.64</v>
+        <v>196.35</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
         <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D20" s="1">
-        <v>45667</v>
+        <v>46013</v>
       </c>
       <c r="E20">
-        <v>1425.1</v>
+        <v>470.23</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s">
         <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D21" s="1">
-        <v>46020</v>
+        <v>46073</v>
       </c>
       <c r="E21">
-        <v>692.28</v>
+        <v>1128.88</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
         <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D22" s="1">
-        <v>45997</v>
+        <v>46109</v>
       </c>
       <c r="E22">
-        <v>2748.24</v>
+        <v>1151.94</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
         <v>52</v>
@@ -1673,15 +1673,15 @@
         <v>273</v>
       </c>
       <c r="D23" s="1">
-        <v>46060</v>
+        <v>46041</v>
       </c>
       <c r="E23">
-        <v>675.13</v>
+        <v>1406.9</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B24" t="s">
         <v>53</v>
@@ -1690,15 +1690,15 @@
         <v>273</v>
       </c>
       <c r="D24" s="1">
-        <v>45791</v>
+        <v>45717</v>
       </c>
       <c r="E24">
-        <v>2208.33</v>
+        <v>1178.99</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
         <v>54</v>
@@ -1707,66 +1707,66 @@
         <v>274</v>
       </c>
       <c r="D25" s="1">
-        <v>45702</v>
+        <v>45674</v>
       </c>
       <c r="E25">
-        <v>2443.29</v>
+        <v>294.41</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
         <v>55</v>
       </c>
       <c r="C26" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D26" s="1">
-        <v>45682</v>
+        <v>45969</v>
       </c>
       <c r="E26">
-        <v>2211.58</v>
+        <v>930.5700000000001</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
         <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D27" s="1">
-        <v>45978</v>
+        <v>45803</v>
       </c>
       <c r="E27">
-        <v>1412.21</v>
+        <v>2448.53</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
         <v>57</v>
       </c>
       <c r="C28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D28" s="1">
-        <v>46082</v>
+        <v>46109</v>
       </c>
       <c r="E28">
-        <v>1445.13</v>
+        <v>914.16</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B29" t="s">
         <v>58</v>
@@ -1775,10 +1775,10 @@
         <v>275</v>
       </c>
       <c r="D29" s="1">
-        <v>45767</v>
+        <v>46066</v>
       </c>
       <c r="E29">
-        <v>2651.21</v>
+        <v>169.49</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1792,32 +1792,32 @@
         <v>273</v>
       </c>
       <c r="D30" s="1">
-        <v>45923</v>
+        <v>46007</v>
       </c>
       <c r="E30">
-        <v>2572.44</v>
+        <v>309.28</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B31" t="s">
         <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D31" s="1">
-        <v>45682</v>
+        <v>45874</v>
       </c>
       <c r="E31">
-        <v>262.54</v>
+        <v>1040.49</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B32" t="s">
         <v>61</v>
@@ -1826,66 +1826,66 @@
         <v>273</v>
       </c>
       <c r="D32" s="1">
-        <v>45661</v>
+        <v>46134</v>
       </c>
       <c r="E32">
-        <v>718.66</v>
+        <v>1739.21</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
         <v>62</v>
       </c>
       <c r="C33" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D33" s="1">
-        <v>45805</v>
+        <v>46003</v>
       </c>
       <c r="E33">
-        <v>965.2</v>
+        <v>1975.1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s">
         <v>63</v>
       </c>
       <c r="C34" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D34" s="1">
-        <v>45665</v>
+        <v>45831</v>
       </c>
       <c r="E34">
-        <v>270.83</v>
+        <v>683.45</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B35" t="s">
         <v>64</v>
       </c>
       <c r="C35" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D35" s="1">
-        <v>45810</v>
+        <v>45741</v>
       </c>
       <c r="E35">
-        <v>170.45</v>
+        <v>1647.83</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B36" t="s">
         <v>65</v>
@@ -1894,15 +1894,15 @@
         <v>275</v>
       </c>
       <c r="D36" s="1">
-        <v>45977</v>
+        <v>46026</v>
       </c>
       <c r="E36">
-        <v>515.48</v>
+        <v>805.39</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B37" t="s">
         <v>66</v>
@@ -1911,10 +1911,10 @@
         <v>273</v>
       </c>
       <c r="D37" s="1">
-        <v>46112</v>
+        <v>45764</v>
       </c>
       <c r="E37">
-        <v>761.03</v>
+        <v>2022.9</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1928,321 +1928,321 @@
         <v>274</v>
       </c>
       <c r="D38" s="1">
-        <v>45907</v>
+        <v>45899</v>
       </c>
       <c r="E38">
-        <v>1459.45</v>
+        <v>128.73</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B39" t="s">
         <v>68</v>
       </c>
       <c r="C39" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D39" s="1">
-        <v>46080</v>
+        <v>45780</v>
       </c>
       <c r="E39">
-        <v>2334.9</v>
+        <v>2522.49</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B40" t="s">
         <v>69</v>
       </c>
       <c r="C40" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D40" s="1">
-        <v>45806</v>
+        <v>46122</v>
       </c>
       <c r="E40">
-        <v>2964.6</v>
+        <v>2047.87</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B41" t="s">
         <v>70</v>
       </c>
       <c r="C41" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D41" s="1">
-        <v>46069</v>
+        <v>45744</v>
       </c>
       <c r="E41">
-        <v>2224.7</v>
+        <v>2023.66</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B42" t="s">
         <v>71</v>
       </c>
       <c r="C42" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D42" s="1">
-        <v>45919</v>
+        <v>46095</v>
       </c>
       <c r="E42">
-        <v>493.53</v>
+        <v>1466.88</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B43" t="s">
         <v>72</v>
       </c>
       <c r="C43" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D43" s="1">
-        <v>46106</v>
+        <v>45760</v>
       </c>
       <c r="E43">
-        <v>260.01</v>
+        <v>1361.37</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B44" t="s">
         <v>73</v>
       </c>
       <c r="C44" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D44" s="1">
-        <v>45688</v>
+        <v>45759</v>
       </c>
       <c r="E44">
-        <v>624.78</v>
+        <v>2820.35</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D45" s="1">
-        <v>46046</v>
+        <v>45798</v>
       </c>
       <c r="E45">
-        <v>2105.98</v>
+        <v>2723.8</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B46" t="s">
         <v>75</v>
       </c>
       <c r="C46" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D46" s="1">
-        <v>45766</v>
+        <v>45920</v>
       </c>
       <c r="E46">
-        <v>664.36</v>
+        <v>2945.45</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B47" t="s">
         <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D47" s="1">
-        <v>45917</v>
+        <v>46105</v>
       </c>
       <c r="E47">
-        <v>1558.07</v>
+        <v>2979.29</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B48" t="s">
         <v>77</v>
       </c>
       <c r="C48" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D48" s="1">
-        <v>45671</v>
+        <v>45743</v>
       </c>
       <c r="E48">
-        <v>843.96</v>
+        <v>2698.13</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B49" t="s">
         <v>78</v>
       </c>
       <c r="C49" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D49" s="1">
-        <v>45932</v>
+        <v>45868</v>
       </c>
       <c r="E49">
-        <v>1190.63</v>
+        <v>1051.24</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B50" t="s">
         <v>79</v>
       </c>
       <c r="C50" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D50" s="1">
-        <v>46068</v>
+        <v>45840</v>
       </c>
       <c r="E50">
-        <v>2281.85</v>
+        <v>2693.94</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B51" t="s">
         <v>80</v>
       </c>
       <c r="C51" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D51" s="1">
-        <v>45856</v>
+        <v>45838</v>
       </c>
       <c r="E51">
-        <v>1656.91</v>
+        <v>2190.9</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B52" t="s">
         <v>81</v>
       </c>
       <c r="C52" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D52" s="1">
-        <v>46012</v>
+        <v>45897</v>
       </c>
       <c r="E52">
-        <v>2844.84</v>
+        <v>1218.77</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B53" t="s">
         <v>82</v>
       </c>
       <c r="C53" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D53" s="1">
-        <v>45675</v>
+        <v>45847</v>
       </c>
       <c r="E53">
-        <v>1648.85</v>
+        <v>1620.94</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
         <v>83</v>
       </c>
       <c r="C54" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D54" s="1">
-        <v>45855</v>
+        <v>45695</v>
       </c>
       <c r="E54">
-        <v>1314.86</v>
+        <v>903.6900000000001</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B55" t="s">
         <v>84</v>
       </c>
       <c r="C55" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D55" s="1">
-        <v>45694</v>
+        <v>45921</v>
       </c>
       <c r="E55">
-        <v>1215.14</v>
+        <v>2842.72</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B56" t="s">
         <v>85</v>
       </c>
       <c r="C56" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D56" s="1">
-        <v>46029</v>
+        <v>45789</v>
       </c>
       <c r="E56">
-        <v>2071.11</v>
+        <v>220.33</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B57" t="s">
         <v>86</v>
@@ -2251,32 +2251,32 @@
         <v>274</v>
       </c>
       <c r="D57" s="1">
-        <v>45810</v>
+        <v>45983</v>
       </c>
       <c r="E57">
-        <v>1033.6</v>
+        <v>1524.42</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B58" t="s">
         <v>87</v>
       </c>
       <c r="C58" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D58" s="1">
-        <v>46079</v>
+        <v>45987</v>
       </c>
       <c r="E58">
-        <v>1962.39</v>
+        <v>2018.64</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B59" t="s">
         <v>88</v>
@@ -2285,10 +2285,10 @@
         <v>275</v>
       </c>
       <c r="D59" s="1">
-        <v>46005</v>
+        <v>45827</v>
       </c>
       <c r="E59">
-        <v>1707.31</v>
+        <v>2046.37</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2299,98 +2299,98 @@
         <v>89</v>
       </c>
       <c r="C60" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D60" s="1">
-        <v>45844</v>
+        <v>45998</v>
       </c>
       <c r="E60">
-        <v>309.62</v>
+        <v>1526.76</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
         <v>90</v>
       </c>
       <c r="C61" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D61" s="1">
-        <v>45695</v>
+        <v>45970</v>
       </c>
       <c r="E61">
-        <v>1300.16</v>
+        <v>2614.35</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
         <v>91</v>
       </c>
       <c r="C62" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D62" s="1">
-        <v>46033</v>
+        <v>45861</v>
       </c>
       <c r="E62">
-        <v>1573.01</v>
+        <v>2042.93</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B63" t="s">
         <v>92</v>
       </c>
       <c r="C63" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D63" s="1">
-        <v>46058</v>
+        <v>45936</v>
       </c>
       <c r="E63">
-        <v>2188.3</v>
+        <v>1422.09</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B64" t="s">
         <v>93</v>
       </c>
       <c r="C64" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D64" s="1">
-        <v>45765</v>
+        <v>45931</v>
       </c>
       <c r="E64">
-        <v>2833.58</v>
+        <v>2110.39</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B65" t="s">
         <v>94</v>
       </c>
       <c r="C65" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D65" s="1">
-        <v>45774</v>
+        <v>45726</v>
       </c>
       <c r="E65">
-        <v>2439.78</v>
+        <v>2358.18</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2401,69 +2401,69 @@
         <v>95</v>
       </c>
       <c r="C66" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D66" s="1">
-        <v>45958</v>
+        <v>46111</v>
       </c>
       <c r="E66">
-        <v>2629.76</v>
+        <v>1600.07</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B67" t="s">
         <v>96</v>
       </c>
       <c r="C67" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D67" s="1">
-        <v>45806</v>
+        <v>45837</v>
       </c>
       <c r="E67">
-        <v>1406.42</v>
+        <v>741.87</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B68" t="s">
         <v>97</v>
       </c>
       <c r="C68" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D68" s="1">
-        <v>45740</v>
+        <v>46140</v>
       </c>
       <c r="E68">
-        <v>968.85</v>
+        <v>2757.71</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B69" t="s">
         <v>98</v>
       </c>
       <c r="C69" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D69" s="1">
-        <v>45767</v>
+        <v>45894</v>
       </c>
       <c r="E69">
-        <v>1813.48</v>
+        <v>1326.86</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B70" t="s">
         <v>99</v>
@@ -2472,15 +2472,15 @@
         <v>275</v>
       </c>
       <c r="D70" s="1">
-        <v>45719</v>
+        <v>46083</v>
       </c>
       <c r="E70">
-        <v>2153.04</v>
+        <v>2244.42</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B71" t="s">
         <v>100</v>
@@ -2489,10 +2489,10 @@
         <v>273</v>
       </c>
       <c r="D71" s="1">
-        <v>46077</v>
+        <v>46003</v>
       </c>
       <c r="E71">
-        <v>1655.87</v>
+        <v>1084.51</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2503,35 +2503,35 @@
         <v>101</v>
       </c>
       <c r="C72" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D72" s="1">
-        <v>45775</v>
+        <v>46069</v>
       </c>
       <c r="E72">
-        <v>1980.19</v>
+        <v>541.33</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B73" t="s">
         <v>102</v>
       </c>
       <c r="C73" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D73" s="1">
-        <v>45852</v>
+        <v>45713</v>
       </c>
       <c r="E73">
-        <v>2328.43</v>
+        <v>352.86</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B74" t="s">
         <v>103</v>
@@ -2540,15 +2540,15 @@
         <v>273</v>
       </c>
       <c r="D74" s="1">
-        <v>45682</v>
+        <v>46027</v>
       </c>
       <c r="E74">
-        <v>1481.49</v>
+        <v>1794.66</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B75" t="s">
         <v>104</v>
@@ -2557,15 +2557,15 @@
         <v>274</v>
       </c>
       <c r="D75" s="1">
-        <v>45868</v>
+        <v>46124</v>
       </c>
       <c r="E75">
-        <v>2536.38</v>
+        <v>692.96</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B76" t="s">
         <v>105</v>
@@ -2574,32 +2574,32 @@
         <v>274</v>
       </c>
       <c r="D76" s="1">
-        <v>45887</v>
+        <v>45740</v>
       </c>
       <c r="E76">
-        <v>675.36</v>
+        <v>1112.73</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B77" t="s">
         <v>106</v>
       </c>
       <c r="C77" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D77" s="1">
-        <v>45890</v>
+        <v>45792</v>
       </c>
       <c r="E77">
-        <v>1915.7</v>
+        <v>2025.91</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B78" t="s">
         <v>107</v>
@@ -2608,32 +2608,32 @@
         <v>275</v>
       </c>
       <c r="D78" s="1">
-        <v>45940</v>
+        <v>45929</v>
       </c>
       <c r="E78">
-        <v>193.03</v>
+        <v>2285.86</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B79" t="s">
         <v>108</v>
       </c>
       <c r="C79" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D79" s="1">
-        <v>45989</v>
+        <v>46026</v>
       </c>
       <c r="E79">
-        <v>586.92</v>
+        <v>2680.73</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B80" t="s">
         <v>109</v>
@@ -2642,10 +2642,10 @@
         <v>275</v>
       </c>
       <c r="D80" s="1">
-        <v>45846</v>
+        <v>46029</v>
       </c>
       <c r="E80">
-        <v>2549.63</v>
+        <v>1908.9</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2656,47 +2656,47 @@
         <v>110</v>
       </c>
       <c r="C81" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D81" s="1">
-        <v>45876</v>
+        <v>45871</v>
       </c>
       <c r="E81">
-        <v>126.82</v>
+        <v>640.6</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B82" t="s">
         <v>111</v>
       </c>
       <c r="C82" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D82" s="1">
-        <v>46112</v>
+        <v>46129</v>
       </c>
       <c r="E82">
-        <v>1267.98</v>
+        <v>2761.56</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B83" t="s">
         <v>112</v>
       </c>
       <c r="C83" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D83" s="1">
-        <v>45731</v>
+        <v>45694</v>
       </c>
       <c r="E83">
-        <v>573.27</v>
+        <v>575.37</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2707,103 +2707,103 @@
         <v>113</v>
       </c>
       <c r="C84" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D84" s="1">
-        <v>45880</v>
+        <v>46100</v>
       </c>
       <c r="E84">
-        <v>1898.46</v>
+        <v>334.58</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B85" t="s">
         <v>114</v>
       </c>
       <c r="C85" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D85" s="1">
-        <v>45738</v>
+        <v>45937</v>
       </c>
       <c r="E85">
-        <v>182.63</v>
+        <v>2766.23</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B86" t="s">
         <v>115</v>
       </c>
       <c r="C86" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D86" s="1">
-        <v>45848</v>
+        <v>46069</v>
       </c>
       <c r="E86">
-        <v>1557.37</v>
+        <v>1005.92</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B87" t="s">
         <v>116</v>
       </c>
       <c r="C87" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D87" s="1">
-        <v>45961</v>
+        <v>45874</v>
       </c>
       <c r="E87">
-        <v>1756</v>
+        <v>959.6799999999999</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
         <v>117</v>
       </c>
       <c r="C88" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D88" s="1">
-        <v>45814</v>
+        <v>45729</v>
       </c>
       <c r="E88">
-        <v>472.18</v>
+        <v>2370.04</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B89" t="s">
         <v>118</v>
       </c>
       <c r="C89" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D89" s="1">
-        <v>45935</v>
+        <v>46039</v>
       </c>
       <c r="E89">
-        <v>1061.58</v>
+        <v>127.27</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B90" t="s">
         <v>119</v>
@@ -2812,27 +2812,27 @@
         <v>273</v>
       </c>
       <c r="D90" s="1">
-        <v>46133</v>
+        <v>46035</v>
       </c>
       <c r="E90">
-        <v>572.1</v>
+        <v>2851.04</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B91" t="s">
         <v>120</v>
       </c>
       <c r="C91" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D91" s="1">
-        <v>45693</v>
+        <v>45776</v>
       </c>
       <c r="E91">
-        <v>1782.85</v>
+        <v>1983.37</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2843,52 +2843,52 @@
         <v>121</v>
       </c>
       <c r="C92" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D92" s="1">
-        <v>45966</v>
+        <v>45752</v>
       </c>
       <c r="E92">
-        <v>1843.93</v>
+        <v>1720.07</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B93" t="s">
         <v>122</v>
       </c>
       <c r="C93" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D93" s="1">
-        <v>46037</v>
+        <v>45905</v>
       </c>
       <c r="E93">
-        <v>691.72</v>
+        <v>2324.82</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B94" t="s">
         <v>123</v>
       </c>
       <c r="C94" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D94" s="1">
-        <v>46030</v>
+        <v>45913</v>
       </c>
       <c r="E94">
-        <v>2498.75</v>
+        <v>1701.34</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B95" t="s">
         <v>124</v>
@@ -2897,32 +2897,32 @@
         <v>273</v>
       </c>
       <c r="D95" s="1">
-        <v>45925</v>
+        <v>45723</v>
       </c>
       <c r="E95">
-        <v>290.03</v>
+        <v>842.7</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B96" t="s">
         <v>125</v>
       </c>
       <c r="C96" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D96" s="1">
-        <v>45966</v>
+        <v>46106</v>
       </c>
       <c r="E96">
-        <v>416.56</v>
+        <v>2842.18</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B97" t="s">
         <v>126</v>
@@ -2931,15 +2931,15 @@
         <v>275</v>
       </c>
       <c r="D97" s="1">
-        <v>45693</v>
+        <v>45773</v>
       </c>
       <c r="E97">
-        <v>1332.67</v>
+        <v>499.94</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B98" t="s">
         <v>127</v>
@@ -2948,15 +2948,15 @@
         <v>275</v>
       </c>
       <c r="D98" s="1">
-        <v>46122</v>
+        <v>46114</v>
       </c>
       <c r="E98">
-        <v>1964.43</v>
+        <v>1848.73</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B99" t="s">
         <v>128</v>
@@ -2965,49 +2965,49 @@
         <v>275</v>
       </c>
       <c r="D99" s="1">
-        <v>45965</v>
+        <v>45942</v>
       </c>
       <c r="E99">
-        <v>2179.06</v>
+        <v>2299.38</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B100" t="s">
         <v>129</v>
       </c>
       <c r="C100" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D100" s="1">
-        <v>45823</v>
+        <v>46019</v>
       </c>
       <c r="E100">
-        <v>2043.33</v>
+        <v>1537.27</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B101" t="s">
         <v>130</v>
       </c>
       <c r="C101" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D101" s="1">
-        <v>45969</v>
+        <v>45942</v>
       </c>
       <c r="E101">
-        <v>1086.36</v>
+        <v>1800.46</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B102" t="s">
         <v>131</v>
@@ -3016,49 +3016,49 @@
         <v>275</v>
       </c>
       <c r="D102" s="1">
-        <v>45729</v>
+        <v>45944</v>
       </c>
       <c r="E102">
-        <v>1257.41</v>
+        <v>2821.62</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B103" t="s">
         <v>132</v>
       </c>
       <c r="C103" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D103" s="1">
-        <v>45780</v>
+        <v>45909</v>
       </c>
       <c r="E103">
-        <v>314.78</v>
+        <v>1082.25</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B104" t="s">
         <v>133</v>
       </c>
       <c r="C104" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D104" s="1">
-        <v>46098</v>
+        <v>45946</v>
       </c>
       <c r="E104">
-        <v>2372.17</v>
+        <v>628.65</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B105" t="s">
         <v>134</v>
@@ -3067,44 +3067,44 @@
         <v>274</v>
       </c>
       <c r="D105" s="1">
-        <v>45777</v>
+        <v>45685</v>
       </c>
       <c r="E105">
-        <v>109.08</v>
+        <v>1959.56</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B106" t="s">
         <v>135</v>
       </c>
       <c r="C106" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D106" s="1">
-        <v>45848</v>
+        <v>45866</v>
       </c>
       <c r="E106">
-        <v>509.81</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B107" t="s">
         <v>136</v>
       </c>
       <c r="C107" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D107" s="1">
-        <v>45892</v>
+        <v>45878</v>
       </c>
       <c r="E107">
-        <v>1023.6</v>
+        <v>1217.24</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -3118,61 +3118,61 @@
         <v>275</v>
       </c>
       <c r="D108" s="1">
-        <v>46088</v>
+        <v>46130</v>
       </c>
       <c r="E108">
-        <v>1485.68</v>
+        <v>660.28</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B109" t="s">
         <v>138</v>
       </c>
       <c r="C109" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D109" s="1">
-        <v>45893</v>
+        <v>46009</v>
       </c>
       <c r="E109">
-        <v>1227.07</v>
+        <v>1851.09</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B110" t="s">
         <v>139</v>
       </c>
       <c r="C110" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D110" s="1">
-        <v>45811</v>
+        <v>46015</v>
       </c>
       <c r="E110">
-        <v>272.57</v>
+        <v>2675.77</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B111" t="s">
         <v>140</v>
       </c>
       <c r="C111" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D111" s="1">
-        <v>45844</v>
+        <v>46084</v>
       </c>
       <c r="E111">
-        <v>2534.26</v>
+        <v>919.49</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3186,15 +3186,15 @@
         <v>274</v>
       </c>
       <c r="D112" s="1">
-        <v>46084</v>
+        <v>45980</v>
       </c>
       <c r="E112">
-        <v>1159.27</v>
+        <v>2645.79</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B113" t="s">
         <v>142</v>
@@ -3203,15 +3203,15 @@
         <v>274</v>
       </c>
       <c r="D113" s="1">
-        <v>45933</v>
+        <v>45836</v>
       </c>
       <c r="E113">
-        <v>695.01</v>
+        <v>1318.16</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B114" t="s">
         <v>143</v>
@@ -3220,49 +3220,49 @@
         <v>273</v>
       </c>
       <c r="D114" s="1">
-        <v>45818</v>
+        <v>46075</v>
       </c>
       <c r="E114">
-        <v>2169.95</v>
+        <v>197.68</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B115" t="s">
         <v>144</v>
       </c>
       <c r="C115" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D115" s="1">
-        <v>45907</v>
+        <v>45851</v>
       </c>
       <c r="E115">
-        <v>341.69</v>
+        <v>1949.26</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B116" t="s">
         <v>145</v>
       </c>
       <c r="C116" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D116" s="1">
-        <v>45932</v>
+        <v>45734</v>
       </c>
       <c r="E116">
-        <v>1096.22</v>
+        <v>2052.28</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B117" t="s">
         <v>146</v>
@@ -3271,32 +3271,32 @@
         <v>275</v>
       </c>
       <c r="D117" s="1">
-        <v>45661</v>
+        <v>45665</v>
       </c>
       <c r="E117">
-        <v>1084.86</v>
+        <v>607.39</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B118" t="s">
         <v>147</v>
       </c>
       <c r="C118" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D118" s="1">
-        <v>45802</v>
+        <v>45794</v>
       </c>
       <c r="E118">
-        <v>2234.53</v>
+        <v>2576.85</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B119" t="s">
         <v>148</v>
@@ -3305,32 +3305,32 @@
         <v>274</v>
       </c>
       <c r="D119" s="1">
-        <v>45848</v>
+        <v>45970</v>
       </c>
       <c r="E119">
-        <v>1776.4</v>
+        <v>518.52</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B120" t="s">
         <v>149</v>
       </c>
       <c r="C120" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D120" s="1">
-        <v>45927</v>
+        <v>46137</v>
       </c>
       <c r="E120">
-        <v>2902.87</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B121" t="s">
         <v>150</v>
@@ -3339,49 +3339,49 @@
         <v>275</v>
       </c>
       <c r="D121" s="1">
-        <v>45918</v>
+        <v>45778</v>
       </c>
       <c r="E121">
-        <v>2455.51</v>
+        <v>2334.93</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B122" t="s">
         <v>151</v>
       </c>
       <c r="C122" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D122" s="1">
-        <v>45696</v>
+        <v>46099</v>
       </c>
       <c r="E122">
-        <v>2881.82</v>
+        <v>2300.12</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B123" t="s">
         <v>152</v>
       </c>
       <c r="C123" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D123" s="1">
-        <v>45716</v>
+        <v>45817</v>
       </c>
       <c r="E123">
-        <v>2000.69</v>
+        <v>1757.77</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B124" t="s">
         <v>153</v>
@@ -3390,100 +3390,100 @@
         <v>273</v>
       </c>
       <c r="D124" s="1">
-        <v>45705</v>
+        <v>45910</v>
       </c>
       <c r="E124">
-        <v>1950.99</v>
+        <v>2775.76</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B125" t="s">
         <v>154</v>
       </c>
       <c r="C125" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D125" s="1">
-        <v>45727</v>
+        <v>46047</v>
       </c>
       <c r="E125">
-        <v>2479.02</v>
+        <v>892.22</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B126" t="s">
         <v>155</v>
       </c>
       <c r="C126" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D126" s="1">
-        <v>45958</v>
+        <v>45726</v>
       </c>
       <c r="E126">
-        <v>2825.43</v>
+        <v>1667.37</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B127" t="s">
         <v>156</v>
       </c>
       <c r="C127" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D127" s="1">
-        <v>46107</v>
+        <v>45954</v>
       </c>
       <c r="E127">
-        <v>2709.61</v>
+        <v>1801.11</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B128" t="s">
         <v>157</v>
       </c>
       <c r="C128" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D128" s="1">
-        <v>46091</v>
+        <v>45996</v>
       </c>
       <c r="E128">
-        <v>1254.78</v>
+        <v>2364.52</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B129" t="s">
         <v>158</v>
       </c>
       <c r="C129" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D129" s="1">
-        <v>45835</v>
+        <v>45941</v>
       </c>
       <c r="E129">
-        <v>443.35</v>
+        <v>538.53</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B130" t="s">
         <v>159</v>
@@ -3492,49 +3492,49 @@
         <v>274</v>
       </c>
       <c r="D130" s="1">
-        <v>45835</v>
+        <v>45832</v>
       </c>
       <c r="E130">
-        <v>2369.93</v>
+        <v>874.97</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B131" t="s">
         <v>160</v>
       </c>
       <c r="C131" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D131" s="1">
-        <v>45918</v>
+        <v>46138</v>
       </c>
       <c r="E131">
-        <v>1532.84</v>
+        <v>574.6</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B132" t="s">
         <v>161</v>
       </c>
       <c r="C132" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D132" s="1">
-        <v>45742</v>
+        <v>45927</v>
       </c>
       <c r="E132">
-        <v>1306.04</v>
+        <v>1323.49</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B133" t="s">
         <v>162</v>
@@ -3543,134 +3543,134 @@
         <v>274</v>
       </c>
       <c r="D133" s="1">
-        <v>45815</v>
+        <v>45805</v>
       </c>
       <c r="E133">
-        <v>1885.28</v>
+        <v>520.2</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B134" t="s">
         <v>163</v>
       </c>
       <c r="C134" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D134" s="1">
-        <v>45706</v>
+        <v>46066</v>
       </c>
       <c r="E134">
-        <v>2686.99</v>
+        <v>1482.92</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B135" t="s">
         <v>164</v>
       </c>
       <c r="C135" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D135" s="1">
-        <v>45750</v>
+        <v>45722</v>
       </c>
       <c r="E135">
-        <v>2343.19</v>
+        <v>232.83</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B136" t="s">
         <v>165</v>
       </c>
       <c r="C136" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D136" s="1">
-        <v>45766</v>
+        <v>45716</v>
       </c>
       <c r="E136">
-        <v>1002.18</v>
+        <v>1297.08</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B137" t="s">
         <v>166</v>
       </c>
       <c r="C137" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D137" s="1">
-        <v>46108</v>
+        <v>45914</v>
       </c>
       <c r="E137">
-        <v>2697</v>
+        <v>304.93</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B138" t="s">
         <v>167</v>
       </c>
       <c r="C138" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D138" s="1">
-        <v>45659</v>
+        <v>45935</v>
       </c>
       <c r="E138">
-        <v>1633.22</v>
+        <v>2600.54</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B139" t="s">
         <v>168</v>
       </c>
       <c r="C139" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D139" s="1">
-        <v>45801</v>
+        <v>46064</v>
       </c>
       <c r="E139">
-        <v>978.1799999999999</v>
+        <v>375.93</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B140" t="s">
         <v>169</v>
       </c>
       <c r="C140" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D140" s="1">
         <v>45999</v>
       </c>
       <c r="E140">
-        <v>494</v>
+        <v>822.6900000000001</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B141" t="s">
         <v>170</v>
@@ -3679,49 +3679,49 @@
         <v>274</v>
       </c>
       <c r="D141" s="1">
-        <v>46036</v>
+        <v>46028</v>
       </c>
       <c r="E141">
-        <v>926.75</v>
+        <v>1784.32</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B142" t="s">
         <v>171</v>
       </c>
       <c r="C142" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D142" s="1">
-        <v>45726</v>
+        <v>45797</v>
       </c>
       <c r="E142">
-        <v>1240.26</v>
+        <v>436.85</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B143" t="s">
         <v>172</v>
       </c>
       <c r="C143" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D143" s="1">
-        <v>46076</v>
+        <v>46008</v>
       </c>
       <c r="E143">
-        <v>437.04</v>
+        <v>2050.15</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B144" t="s">
         <v>173</v>
@@ -3730,15 +3730,15 @@
         <v>273</v>
       </c>
       <c r="D144" s="1">
-        <v>45692</v>
+        <v>45747</v>
       </c>
       <c r="E144">
-        <v>2966.42</v>
+        <v>2537.07</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B145" t="s">
         <v>174</v>
@@ -3747,49 +3747,49 @@
         <v>273</v>
       </c>
       <c r="D145" s="1">
-        <v>45799</v>
+        <v>46037</v>
       </c>
       <c r="E145">
-        <v>2517.78</v>
+        <v>1963.32</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B146" t="s">
         <v>175</v>
       </c>
       <c r="C146" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D146" s="1">
-        <v>45818</v>
+        <v>45761</v>
       </c>
       <c r="E146">
-        <v>195.39</v>
+        <v>1425.04</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B147" t="s">
         <v>176</v>
       </c>
       <c r="C147" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D147" s="1">
-        <v>45681</v>
+        <v>46044</v>
       </c>
       <c r="E147">
-        <v>2986.69</v>
+        <v>1322.6</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B148" t="s">
         <v>177</v>
@@ -3798,10 +3798,10 @@
         <v>275</v>
       </c>
       <c r="D148" s="1">
-        <v>46141</v>
+        <v>46055</v>
       </c>
       <c r="E148">
-        <v>2562.82</v>
+        <v>2138.58</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -3812,30 +3812,30 @@
         <v>178</v>
       </c>
       <c r="C149" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D149" s="1">
-        <v>45792</v>
+        <v>45670</v>
       </c>
       <c r="E149">
-        <v>1629.71</v>
+        <v>947.05</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B150" t="s">
         <v>179</v>
       </c>
       <c r="C150" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D150" s="1">
-        <v>46071</v>
+        <v>46011</v>
       </c>
       <c r="E150">
-        <v>2396.65</v>
+        <v>1819.56</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -3846,103 +3846,103 @@
         <v>180</v>
       </c>
       <c r="C151" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D151" s="1">
-        <v>45847</v>
+        <v>46119</v>
       </c>
       <c r="E151">
-        <v>909.75</v>
+        <v>2100.16</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B152" t="s">
         <v>181</v>
       </c>
       <c r="C152" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D152" s="1">
-        <v>46014</v>
+        <v>45852</v>
       </c>
       <c r="E152">
-        <v>179.63</v>
+        <v>1751.66</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B153" t="s">
         <v>182</v>
       </c>
       <c r="C153" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D153" s="1">
-        <v>45861</v>
+        <v>46001</v>
       </c>
       <c r="E153">
-        <v>1315.03</v>
+        <v>1107.98</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B154" t="s">
         <v>183</v>
       </c>
       <c r="C154" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D154" s="1">
-        <v>46102</v>
+        <v>45846</v>
       </c>
       <c r="E154">
-        <v>203.08</v>
+        <v>2922.86</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B155" t="s">
         <v>184</v>
       </c>
       <c r="C155" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D155" s="1">
-        <v>46008</v>
+        <v>45896</v>
       </c>
       <c r="E155">
-        <v>1410.64</v>
+        <v>2349.88</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B156" t="s">
         <v>185</v>
       </c>
       <c r="C156" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D156" s="1">
-        <v>46007</v>
+        <v>45735</v>
       </c>
       <c r="E156">
-        <v>1097.09</v>
+        <v>2515.86</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B157" t="s">
         <v>186</v>
@@ -3951,32 +3951,32 @@
         <v>274</v>
       </c>
       <c r="D157" s="1">
-        <v>45989</v>
+        <v>45986</v>
       </c>
       <c r="E157">
-        <v>2490.98</v>
+        <v>1081.8</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B158" t="s">
         <v>187</v>
       </c>
       <c r="C158" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D158" s="1">
-        <v>45925</v>
+        <v>45763</v>
       </c>
       <c r="E158">
-        <v>946.78</v>
+        <v>270.3</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B159" t="s">
         <v>188</v>
@@ -3985,15 +3985,15 @@
         <v>274</v>
       </c>
       <c r="D159" s="1">
-        <v>46064</v>
+        <v>45847</v>
       </c>
       <c r="E159">
-        <v>1675.4</v>
+        <v>1693.65</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B160" t="s">
         <v>189</v>
@@ -4002,49 +4002,49 @@
         <v>274</v>
       </c>
       <c r="D160" s="1">
-        <v>46004</v>
+        <v>45789</v>
       </c>
       <c r="E160">
-        <v>902.29</v>
+        <v>877.51</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B161" t="s">
         <v>190</v>
       </c>
       <c r="C161" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D161" s="1">
-        <v>45836</v>
+        <v>45784</v>
       </c>
       <c r="E161">
-        <v>105.29</v>
+        <v>1976.7</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B162" t="s">
         <v>191</v>
       </c>
       <c r="C162" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D162" s="1">
-        <v>45889</v>
+        <v>45695</v>
       </c>
       <c r="E162">
-        <v>813.62</v>
+        <v>2105.9</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B163" t="s">
         <v>192</v>
@@ -4053,32 +4053,32 @@
         <v>274</v>
       </c>
       <c r="D163" s="1">
-        <v>45808</v>
+        <v>45727</v>
       </c>
       <c r="E163">
-        <v>1878.95</v>
+        <v>2988.62</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B164" t="s">
         <v>193</v>
       </c>
       <c r="C164" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D164" s="1">
-        <v>46088</v>
+        <v>45872</v>
       </c>
       <c r="E164">
-        <v>1900.6</v>
+        <v>808.54</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B165" t="s">
         <v>194</v>
@@ -4087,15 +4087,15 @@
         <v>275</v>
       </c>
       <c r="D165" s="1">
-        <v>45680</v>
+        <v>45911</v>
       </c>
       <c r="E165">
-        <v>1051.92</v>
+        <v>1597.38</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B166" t="s">
         <v>195</v>
@@ -4104,15 +4104,15 @@
         <v>273</v>
       </c>
       <c r="D166" s="1">
-        <v>46085</v>
+        <v>45960</v>
       </c>
       <c r="E166">
-        <v>707.61</v>
+        <v>689.4</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B167" t="s">
         <v>196</v>
@@ -4121,112 +4121,112 @@
         <v>274</v>
       </c>
       <c r="D167" s="1">
-        <v>45712</v>
+        <v>46035</v>
       </c>
       <c r="E167">
-        <v>902.02</v>
+        <v>1025.88</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B168" t="s">
         <v>197</v>
       </c>
       <c r="C168" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D168" s="1">
-        <v>45825</v>
+        <v>46039</v>
       </c>
       <c r="E168">
-        <v>1453.91</v>
+        <v>1286.52</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B169" t="s">
         <v>198</v>
       </c>
       <c r="C169" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D169" s="1">
-        <v>46071</v>
+        <v>45941</v>
       </c>
       <c r="E169">
-        <v>1850.37</v>
+        <v>1146.05</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B170" t="s">
         <v>199</v>
       </c>
       <c r="C170" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D170" s="1">
-        <v>46037</v>
+        <v>46039</v>
       </c>
       <c r="E170">
-        <v>103.9</v>
+        <v>1899.31</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B171" t="s">
         <v>200</v>
       </c>
       <c r="C171" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D171" s="1">
-        <v>46094</v>
+        <v>46103</v>
       </c>
       <c r="E171">
-        <v>143.7</v>
+        <v>2277.79</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B172" t="s">
         <v>201</v>
       </c>
       <c r="C172" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D172" s="1">
-        <v>45806</v>
+        <v>45930</v>
       </c>
       <c r="E172">
-        <v>2673.01</v>
+        <v>1821.57</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B173" t="s">
         <v>202</v>
       </c>
       <c r="C173" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D173" s="1">
-        <v>46119</v>
+        <v>46066</v>
       </c>
       <c r="E173">
-        <v>2948.69</v>
+        <v>1458.02</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -4240,32 +4240,32 @@
         <v>274</v>
       </c>
       <c r="D174" s="1">
-        <v>45782</v>
+        <v>46104</v>
       </c>
       <c r="E174">
-        <v>187.14</v>
+        <v>1443.49</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B175" t="s">
         <v>204</v>
       </c>
       <c r="C175" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D175" s="1">
-        <v>46109</v>
+        <v>45762</v>
       </c>
       <c r="E175">
-        <v>2289.46</v>
+        <v>670.0700000000001</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B176" t="s">
         <v>205</v>
@@ -4274,151 +4274,151 @@
         <v>275</v>
       </c>
       <c r="D176" s="1">
-        <v>45726</v>
+        <v>45920</v>
       </c>
       <c r="E176">
-        <v>1409.18</v>
+        <v>444.81</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B177" t="s">
         <v>206</v>
       </c>
       <c r="C177" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D177" s="1">
-        <v>45984</v>
+        <v>46101</v>
       </c>
       <c r="E177">
-        <v>906.36</v>
+        <v>1900.3</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B178" t="s">
         <v>207</v>
       </c>
       <c r="C178" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D178" s="1">
-        <v>45856</v>
+        <v>46047</v>
       </c>
       <c r="E178">
-        <v>2372.85</v>
+        <v>1584.95</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B179" t="s">
         <v>208</v>
       </c>
       <c r="C179" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D179" s="1">
-        <v>45895</v>
+        <v>45761</v>
       </c>
       <c r="E179">
-        <v>703.13</v>
+        <v>1404.97</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B180" t="s">
         <v>209</v>
       </c>
       <c r="C180" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D180" s="1">
-        <v>46121</v>
+        <v>45702</v>
       </c>
       <c r="E180">
-        <v>2715.51</v>
+        <v>2900.13</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B181" t="s">
         <v>210</v>
       </c>
       <c r="C181" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D181" s="1">
-        <v>45985</v>
+        <v>45928</v>
       </c>
       <c r="E181">
-        <v>666.64</v>
+        <v>1062.27</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B182" t="s">
         <v>211</v>
       </c>
       <c r="C182" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D182" s="1">
-        <v>45869</v>
+        <v>45718</v>
       </c>
       <c r="E182">
-        <v>955.4400000000001</v>
+        <v>1650.61</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B183" t="s">
         <v>212</v>
       </c>
       <c r="C183" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D183" s="1">
-        <v>45976</v>
+        <v>45783</v>
       </c>
       <c r="E183">
-        <v>855.66</v>
+        <v>862.83</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B184" t="s">
         <v>213</v>
       </c>
       <c r="C184" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D184" s="1">
-        <v>45690</v>
+        <v>45868</v>
       </c>
       <c r="E184">
-        <v>2817.41</v>
+        <v>312.37</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B185" t="s">
         <v>214</v>
@@ -4427,15 +4427,15 @@
         <v>274</v>
       </c>
       <c r="D185" s="1">
-        <v>45825</v>
+        <v>45844</v>
       </c>
       <c r="E185">
-        <v>2368.89</v>
+        <v>572.27</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B186" t="s">
         <v>215</v>
@@ -4444,49 +4444,49 @@
         <v>273</v>
       </c>
       <c r="D186" s="1">
-        <v>45758</v>
+        <v>45874</v>
       </c>
       <c r="E186">
-        <v>1617.72</v>
+        <v>1081.19</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B187" t="s">
         <v>216</v>
       </c>
       <c r="C187" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D187" s="1">
-        <v>45757</v>
+        <v>45828</v>
       </c>
       <c r="E187">
-        <v>2202.57</v>
+        <v>2498.24</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B188" t="s">
         <v>217</v>
       </c>
       <c r="C188" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D188" s="1">
-        <v>45786</v>
+        <v>46038</v>
       </c>
       <c r="E188">
-        <v>2466.7</v>
+        <v>2314.65</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B189" t="s">
         <v>218</v>
@@ -4495,27 +4495,27 @@
         <v>273</v>
       </c>
       <c r="D189" s="1">
-        <v>45827</v>
+        <v>46125</v>
       </c>
       <c r="E189">
-        <v>2179.22</v>
+        <v>1698.22</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B190" t="s">
         <v>219</v>
       </c>
       <c r="C190" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D190" s="1">
-        <v>46057</v>
+        <v>45770</v>
       </c>
       <c r="E190">
-        <v>2507.79</v>
+        <v>2565.03</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -4526,13 +4526,13 @@
         <v>220</v>
       </c>
       <c r="C191" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D191" s="1">
-        <v>46089</v>
+        <v>45943</v>
       </c>
       <c r="E191">
-        <v>2405.81</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -4543,18 +4543,18 @@
         <v>221</v>
       </c>
       <c r="C192" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D192" s="1">
-        <v>45937</v>
+        <v>45719</v>
       </c>
       <c r="E192">
-        <v>174.74</v>
+        <v>189.62</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B193" t="s">
         <v>222</v>
@@ -4563,32 +4563,32 @@
         <v>274</v>
       </c>
       <c r="D193" s="1">
-        <v>45856</v>
+        <v>45953</v>
       </c>
       <c r="E193">
-        <v>1251.88</v>
+        <v>107.03</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B194" t="s">
         <v>223</v>
       </c>
       <c r="C194" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D194" s="1">
-        <v>45970</v>
+        <v>45904</v>
       </c>
       <c r="E194">
-        <v>114.26</v>
+        <v>385.66</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B195" t="s">
         <v>224</v>
@@ -4597,32 +4597,32 @@
         <v>274</v>
       </c>
       <c r="D195" s="1">
-        <v>46098</v>
+        <v>46017</v>
       </c>
       <c r="E195">
-        <v>2402.15</v>
+        <v>974.0700000000001</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B196" t="s">
         <v>225</v>
       </c>
       <c r="C196" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D196" s="1">
-        <v>45738</v>
+        <v>45894</v>
       </c>
       <c r="E196">
-        <v>1298.86</v>
+        <v>1396.47</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B197" t="s">
         <v>226</v>
@@ -4631,15 +4631,15 @@
         <v>275</v>
       </c>
       <c r="D197" s="1">
-        <v>45851</v>
+        <v>45821</v>
       </c>
       <c r="E197">
-        <v>2869.07</v>
+        <v>1741.05</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B198" t="s">
         <v>227</v>
@@ -4648,15 +4648,15 @@
         <v>273</v>
       </c>
       <c r="D198" s="1">
-        <v>45959</v>
+        <v>46031</v>
       </c>
       <c r="E198">
-        <v>2422.44</v>
+        <v>1861.37</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B199" t="s">
         <v>228</v>
@@ -4665,15 +4665,15 @@
         <v>274</v>
       </c>
       <c r="D199" s="1">
-        <v>45832</v>
+        <v>45724</v>
       </c>
       <c r="E199">
-        <v>848.52</v>
+        <v>1921.8</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B200" t="s">
         <v>229</v>
@@ -4682,49 +4682,49 @@
         <v>274</v>
       </c>
       <c r="D200" s="1">
-        <v>45664</v>
+        <v>45819</v>
       </c>
       <c r="E200">
-        <v>2480.81</v>
+        <v>201.62</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B201" t="s">
         <v>230</v>
       </c>
       <c r="C201" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D201" s="1">
-        <v>45929</v>
+        <v>45999</v>
       </c>
       <c r="E201">
-        <v>1717.41</v>
+        <v>1003.02</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B202" t="s">
         <v>231</v>
       </c>
       <c r="C202" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D202" s="1">
-        <v>45824</v>
+        <v>46109</v>
       </c>
       <c r="E202">
-        <v>2602.91</v>
+        <v>2773.3</v>
       </c>
     </row>
     <row r="203" spans="1:5">
       <c r="A203" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B203" t="s">
         <v>232</v>
@@ -4733,66 +4733,66 @@
         <v>273</v>
       </c>
       <c r="D203" s="1">
-        <v>46088</v>
+        <v>45860</v>
       </c>
       <c r="E203">
-        <v>2942.43</v>
+        <v>1811.6</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B204" t="s">
         <v>233</v>
       </c>
       <c r="C204" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D204" s="1">
-        <v>45951</v>
+        <v>46142</v>
       </c>
       <c r="E204">
-        <v>1505.57</v>
+        <v>116.44</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B205" t="s">
         <v>234</v>
       </c>
       <c r="C205" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D205" s="1">
-        <v>45752</v>
+        <v>45792</v>
       </c>
       <c r="E205">
-        <v>2601.79</v>
+        <v>1141.22</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B206" t="s">
         <v>235</v>
       </c>
       <c r="C206" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D206" s="1">
-        <v>45671</v>
+        <v>46013</v>
       </c>
       <c r="E206">
-        <v>2847.08</v>
+        <v>1078.45</v>
       </c>
     </row>
     <row r="207" spans="1:5">
       <c r="A207" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B207" t="s">
         <v>236</v>
@@ -4801,15 +4801,15 @@
         <v>273</v>
       </c>
       <c r="D207" s="1">
-        <v>45889</v>
+        <v>45834</v>
       </c>
       <c r="E207">
-        <v>446.46</v>
+        <v>832.84</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B208" t="s">
         <v>237</v>
@@ -4818,32 +4818,32 @@
         <v>275</v>
       </c>
       <c r="D208" s="1">
-        <v>45898</v>
+        <v>45887</v>
       </c>
       <c r="E208">
-        <v>529.11</v>
+        <v>2180.7</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B209" t="s">
         <v>238</v>
       </c>
       <c r="C209" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D209" s="1">
-        <v>45677</v>
+        <v>45721</v>
       </c>
       <c r="E209">
-        <v>1807.16</v>
+        <v>590.48</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B210" t="s">
         <v>239</v>
@@ -4852,27 +4852,27 @@
         <v>273</v>
       </c>
       <c r="D210" s="1">
-        <v>46127</v>
+        <v>45814</v>
       </c>
       <c r="E210">
-        <v>2833.15</v>
+        <v>1106.06</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B211" t="s">
         <v>240</v>
       </c>
       <c r="C211" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D211" s="1">
-        <v>45716</v>
+        <v>45839</v>
       </c>
       <c r="E211">
-        <v>1070.77</v>
+        <v>2655.25</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -5189,7 +5189,7 @@
         <v>259</v>
       </c>
       <c r="C230" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D230" t="s">
         <v>299</v>
@@ -5206,7 +5206,7 @@
         <v>260</v>
       </c>
       <c r="C231" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D231" t="s">
         <v>300</v>
@@ -5240,7 +5240,7 @@
         <v>262</v>
       </c>
       <c r="C233" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D233" t="s">
         <v>302</v>
@@ -5319,7 +5319,7 @@
     </row>
     <row r="238" spans="1:5">
       <c r="A238" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B238" t="s">
         <v>267</v>
